--- a/demo/tlp-uploads/DSA_FJ-III_I5.xlsx
+++ b/demo/tlp-uploads/DSA_FJ-III_I5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TLP5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLP5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21CSC201J(Data Structures and Algorithms) handled by Mr. Varsha Kumar(902049)</t>
+          <t>21CSC201J(Data Structures and Algorithms) handled by Shaurya Pandey(902049)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RA2411999002517</t>
+          <t>RA2411999002519</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -521,12 +521,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RA2411999002518</t>
+          <t>RA2411999002520</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.67</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RA2411999002519</t>
+          <t>RA2411999002521</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>30.00</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RA2411999002520</t>
+          <t>RA2411999002522</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.00</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RA2411999002521</t>
+          <t>RA2411999002523</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>40.00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RA2411999002522</t>
+          <t>RA2411999002524</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>46.67</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RA2411999002523</t>
+          <t>RA2411999002525</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RA2411999002524</t>
+          <t>RA2411999002526</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>53.33</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RA2411999002525</t>
+          <t>RA2411999002527</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>50.00</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RA2411999002526</t>
+          <t>RA2411999002528</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>53.33</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RA2411999002527</t>
+          <t>RA2411999002529</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>70.00</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RA2411999002528</t>
+          <t>RA2411999002530</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>83.33</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RA2411999002529</t>
+          <t>RA2411999002531</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>56.67</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RA2411999002530</t>
+          <t>RA2411999002532</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RA2411999002531</t>
+          <t>RA2411999002533</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RA2411999002532</t>
+          <t>RA2411999002534</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RA2411999002533</t>
+          <t>RA2411999002535</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>46.67</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RA2411999002534</t>
+          <t>RA2411999002536</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>66.67</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RA2411999002535</t>
+          <t>RA2411999002537</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>76.67</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RA2411999002536</t>
+          <t>RA2411999002538</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>76.67</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RA2411999002537</t>
+          <t>RA2411999002539</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>63.33</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RA2411999002538</t>
+          <t>RA2411999002540</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>50.00</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RA2411999002539</t>
+          <t>RA2411999002541</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>63.33</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RA2411999002540</t>
+          <t>RA2411999002542</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RA2411999002541</t>
+          <t>RA2411999002543</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RA2411999002542</t>
+          <t>RA2411999002544</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>36.67</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RA2411999002543</t>
+          <t>RA2411999002545</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.33</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RA2411999002544</t>
+          <t>RA2411999002546</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>76.67</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RA2411999002545</t>
+          <t>RA2411999002547</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>80.00</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RA2411999002546</t>
+          <t>RA2411999002548</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>73.33</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RA2411999002547</t>
+          <t>RA2411999002549</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>56.67</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RA2411999002548</t>
+          <t>RA2411999002550</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>56.67</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RA2411999002549</t>
+          <t>RA2411999002551</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RA2411999002550</t>
+          <t>RA2411999002552</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RA2411999002551</t>
+          <t>RA2411999002553</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>43.33</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RA2411999002552</t>
+          <t>RA2411999002554</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>86.67</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RA2411999002553</t>
+          <t>RA2411999002555</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RA2411999002554</t>
+          <t>RA2411999002556</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>76.67</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RA2411999002555</t>
+          <t>RA2411999002557</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>70.00</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RA2411999002556</t>
+          <t>RA2411999002558</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>60.00</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
